--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Sally Mugabe CH Admission - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Sally Mugabe CH Admission - metadata.xlsx
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="V4" t="str">
-        <v>{"actionText":"RESUSCITATION","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Resuscitate the baby:","title2":"How to use Bag-Valve-Mask:","title3":"When stable continue with Neotree","title4":"","text1":"","text2":"","text3":"If no HR for &gt; 10 minutes or remains &lt; 60/min for 20 mins STOP resuscitating but CONTINUE with Neotree","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://zim-dev-webeditor.neotree.org/files/40504d7d-49d5-4da9-9208-9381c8389407?height=1076&amp;width=588","fileId":"40504d7d-49d5-4da9-9208-9381c8389407","filename":"HBB action plan.jpg","size":"84101"},"image2":{"data":"https://zim-dev-webeditor.neotree.org/files/e6cfc315-e108-4af8-9cb8-d4a9a2b70e42?height=312&amp;width=320","fileId":"e6cfc315-e108-4af8-9cb8-d4a9a2b70e42","filename":"BVMblue.png","size":"89015"},"image3":{"data":"https://zim-webeditor.neotree.org:10243/files/ce56c84f-4fac-44a7-8c22-05e3fe1275f1?height=609&amp;width=738","fileId":"ce56c84f-4fac-44a7-8c22-05e3fe1275f1","filename":"ce56c84f-4fac-44a7-8c22-05e3fe1275f1__Resus.png?w=738&amp;h=609","size":337864,"contentType":"image/png"}}}</v>
+        <v>{"actionText":"RESUSCITATION","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Resuscitate the baby:","title2":"How to use Bag-Valve-Mask:","title3":"When stable continue with Neotree","title4":"","text1":"","text2":"","text3":"If no HR for &gt; 10 minutes or remains &lt; 60/min for 20 mins STOP resuscitating but CONTINUE with Neotree","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://zim-dev-webeditor.neotree.org/files/40504d7d-49d5-4da9-9208-9381c8389407?height=1076&amp;width=588","fileId":"40504d7d-49d5-4da9-9208-9381c8389407","filename":"HBB action plan.jpg","size":"84101"},"image2":{"data":"https://zim-dev-webeditor.neotree.org/files/e6cfc315-e108-4af8-9cb8-d4a9a2b70e42?height=312&amp;width=320","fileId":"e6cfc315-e108-4af8-9cb8-d4a9a2b70e42","filename":"BVMblue.png","size":"89015"},"image3":{"data":"https://zim-dev-webeditor.neotree.org/files/4035e5e1-d8b1-4279-b4f0-5b401268e62d","fileId":"4035e5e1-d8b1-4279-b4f0-5b401268e62d","filename":"4035e5e1-d8b1-4279-b4f0-5b401268e62d__Resus algorithm.jpg?w=1131&amp;h=1600","size":193621,"contentType":"image/jpeg"}}}</v>
       </c>
     </row>
     <row r="5">
@@ -1668,7 +1668,7 @@
         <v/>
       </c>
       <c r="O19" t="str">
-        <v>($NoPulseOx = false and $SatsAir &lt; 90) or ($NoPulseOx = false and $RR &gt; 60)</v>
+        <v>$SatsAir &lt; 90 or $RR &gt; 60</v>
       </c>
       <c r="P19" t="str">
         <v/>
@@ -2460,7 +2460,7 @@
         <v>BloodSugarmmol</v>
       </c>
       <c r="G31" t="str">
-        <v>Blood Sugar (mmol/L)      (2.5 - 4.5)</v>
+        <v>Blood Sugar (mmol/L)      (2.6 - 8.3)</v>
       </c>
       <c r="H31" t="str">
         <v>number</v>
@@ -2614,13 +2614,13 @@
         <v>No</v>
       </c>
       <c r="M33" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="N33" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O33" t="str">
-        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 46.8</v>
+        <v>$BloodSugarmmol &lt; 2.6 or $BloodSugarmg &lt; 47</v>
       </c>
       <c r="P33" t="str">
         <v/>
@@ -3093,7 +3093,7 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Prematurity"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Syph_Exp","valueLabel":"Syphillis Exposure"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Suspected neonatal sepsis"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Convulsions","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty in breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"FD","valueLabel":"Not sucking / feeding difficulties"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"NE","valueLabel":"Neonatal encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LowBirthWeight","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium Aspiration"},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida"},{"value":"Prem","valueLabel":"Premature"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Severe Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Other congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Syph_Exp","valueLabel":"Syphillis Exposure"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Sepsis suspected"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -3161,7 +3161,7 @@
         <v/>
       </c>
       <c r="N41" t="str">
-        <v>[{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Cong","valueLabel":"Other Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AD","valueLabel":"Abdominal distension","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fev","valueLabel":"Fever","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic ischaemic encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVX","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low birth weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mec","valueLabel":"Possible Meconium aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OM","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pneum","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -3430,7 +3430,7 @@
         <v>No</v>
       </c>
       <c r="M45" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>$AdmReasonAdd != 'DU'</v>
       </c>
       <c r="N45" t="str">
         <v/>
@@ -3498,7 +3498,7 @@
         <v>No</v>
       </c>
       <c r="M46" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N46" t="str">
         <v/>
@@ -3566,7 +3566,7 @@
         <v>No</v>
       </c>
       <c r="M47" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N47" t="str">
         <v/>
@@ -4160,7 +4160,7 @@
         <v>Gestation</v>
       </c>
       <c r="G56" t="str">
-        <v>Gestational age at birth (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H56" t="str">
         <v>number</v>
@@ -4660,7 +4660,7 @@
         <v/>
       </c>
       <c r="O63" t="str" xml:space="preserve">
-        <v xml:space="preserve">!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')
+        <v xml:space="preserve">!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])
 $AdmReason != 'BBA'</v>
       </c>
       <c r="P63" t="str">
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="O64" t="str" xml:space="preserve">
-        <v xml:space="preserve">!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')
+        <v xml:space="preserve">!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])
 $AdmReason != 'BBA'</v>
       </c>
       <c r="P64" t="str">
@@ -4798,7 +4798,7 @@
         <v/>
       </c>
       <c r="O65" t="str" xml:space="preserve">
-        <v xml:space="preserve">!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')
+        <v xml:space="preserve">!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])
 $AdmReason != 'BBA'</v>
       </c>
       <c r="P65" t="str">
@@ -7448,7 +7448,7 @@
         <v>$FeverSR = true</v>
       </c>
       <c r="N104" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O104" t="str">
         <v>$FeverSR = true</v>
@@ -7584,7 +7584,7 @@
         <v>$RespSR != 'Norm'</v>
       </c>
       <c r="N106" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O106" t="str">
         <v>$RespSR != 'Norm'</v>
@@ -7720,7 +7720,7 @@
         <v>$Vomiting != 'Norm'</v>
       </c>
       <c r="N108" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O108" t="str">
         <v>$Vomiting != 'Norm'</v>
@@ -8060,7 +8060,7 @@
         <v>$Age &gt; 47.9 or $AgeEstimate = 'INF72' or $AgeEstimate = 'INF'</v>
       </c>
       <c r="N113" t="str">
-        <v>[{"value":"Norm","valueLabel":"Passing urine normally"},{"value":"NoPU","valueLabel":"Not passing urine"}]</v>
+        <v>[{"value":"Norm","valueLabel":"Passing urine normally"}]</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -8196,7 +8196,7 @@
         <v>$SRNeuroOther != 'Norm'</v>
       </c>
       <c r="N115" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O115" t="str">
         <v>$SRNeuroOther != 'Norm'</v>
@@ -8941,13 +8941,13 @@
         <v>No</v>
       </c>
       <c r="M126" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N126" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O126" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P126" t="str">
         <v/>
@@ -9083,7 +9083,7 @@
         <v>[{"value":"HA","valueLabel":"Harare"},{"value":"BU","valueLabel":"Bulawayo"},{"value":"MC","valueLabel":"Mashonaland Central"},{"value":"ME","valueLabel":"Mashonaland East"},{"value":"MW","valueLabel":"Mashonaland West"},{"value":"MA","valueLabel":"Manicaland"},{"value":"MAS","valueLabel":"Masvingo"},{"value":"MN","valueLabel":"Matabeleland North"},{"value":"MS","valueLabel":"Matabeleland South"},{"value":"MID","valueLabel":"Midlands"}]</v>
       </c>
       <c r="O128" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P128" t="str">
         <v/>
@@ -9151,7 +9151,7 @@
         <v>[{"value":"Av","valueLabel":"Avondale"},{"value":"Be","valueLabel":"Belvedere"},{"value":"Bo","valueLabel":"Borrowdale"},{"value":"Bu","valueLabel":"Budiriro"},{"value":"CH","valueLabel":"Chitungwiza"},{"value":"Dz","valueLabel":"Dzivaresekwa"},{"value":"EP","valueLabel":"Epworth"},{"value":"GLN","valueLabel":"Glen Norah"},{"value":"GLV","valueLabel":"Glen View"},{"value":"Gr","valueLabel":"Greendale"},{"value":"Ha","valueLabel":"Hatfield"},{"value":"Hat","valueLabel":"Hatcliffe"},{"value":"HC","valueLabel":"Harare Central"},{"value":"Hi","valueLabel":"Highlands"},{"value":"Hif","valueLabel":"Highfield"},{"value":"Ho","valueLabel":"Hopley"},{"value":"Ka","valueLabel":"Kambuzuma"},{"value":"Ku","valueLabel":"Kuwadzana"},{"value":"Ma","valueLabel":"Mabelreign"},{"value":"Mar","valueLabel":"Marlborough"},{"value":"Mab","valueLabel":"Mabvuku"},{"value":"Mb","valueLabel":"Mbare"},{"value":"Mo","valueLabel":"Mount Pleasant"},{"value":"Mu","valueLabel":"Mufakose"},{"value":"So","valueLabel":"Southerton"},{"value":"Su","valueLabel":"Sunningdale"},{"value":"Ta","valueLabel":"Tafara"},{"value":"Wa","valueLabel":"Warren Park"},{"value":"Wat","valueLabel":"Waterfalls"},{"value":"OT","valueLabel":"Other"}]</v>
       </c>
       <c r="O129" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P129" t="str">
         <v/>
@@ -9219,7 +9219,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"}]</v>
       </c>
       <c r="O130" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P130" t="str">
         <v/>
@@ -9287,7 +9287,7 @@
         <v/>
       </c>
       <c r="O131" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P131" t="str">
         <v/>
@@ -9355,7 +9355,7 @@
         <v/>
       </c>
       <c r="O132" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P132" t="str">
         <v/>
@@ -9417,13 +9417,13 @@
         <v>No</v>
       </c>
       <c r="M133" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N133" t="str">
         <v>[{"value":"MAR","valueLabel":"Married","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DIV","valueLabel":"Divorced","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"WID","valueLabel":"Widowed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S","valueLabel":"Single","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O133" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P133" t="str">
         <v/>
@@ -9488,10 +9488,10 @@
         <v/>
       </c>
       <c r="N134" t="str">
-        <v>[{"value":"A","valueLabel":"African"},{"value":"AA","valueLabel":"African/AfricanAmerican"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"A","valueLabel":"African"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O134" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P134" t="str">
         <v/>
@@ -9559,7 +9559,7 @@
         <v/>
       </c>
       <c r="O135" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P135" t="str">
         <v/>
@@ -9621,13 +9621,13 @@
         <v>No</v>
       </c>
       <c r="M136" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N136" t="str">
         <v>[{"value":"A","valueLabel":"Anglican (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apostolic (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ba","valueLabel":"Baptist (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PE","valueLabel":"Pentecostal (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"P","valueLabel":"Prespyterian (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SDA","valueLabel":"Seventh Day Adventist (SDA) (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CP","valueLabel":"Other Christian Protestant","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RC","valueLabel":"Roman Catholic (Christian)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"J","valueLabel":"Jewish","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehova's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AG","valueLabel":"Agnostic","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Z","valueLabel":"Zion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O136" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P136" t="str">
         <v/>
@@ -9757,13 +9757,13 @@
         <v>No</v>
       </c>
       <c r="M138" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N138" t="str">
         <v>[{"value":"true","valueLabel":"Yes"},{"value":"false","valueLabel":"No"}]</v>
       </c>
       <c r="O138" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P138" t="str">
         <v/>
@@ -9890,7 +9890,7 @@
         <v>Yes</v>
       </c>
       <c r="L140" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M140" t="str">
         <v/>
@@ -10011,7 +10011,7 @@
         <v>HIVtestResult</v>
       </c>
       <c r="G142" t="str">
-        <v>What was the Result?</v>
+        <v>HIV test result</v>
       </c>
       <c r="H142" t="str">
         <v>dropdown</v>
@@ -10032,7 +10032,7 @@
         <v/>
       </c>
       <c r="N142" t="str">
-        <v>[{"value":"R","valueLabel":"Positive"},{"value":"NR","valueLabel":"Negative"},{"value":"U","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"R","valueLabel":"Positive"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O142" t="str">
         <v>$MatHIVtest = true</v>
@@ -10144,7 +10144,7 @@
         <v>form</v>
       </c>
       <c r="F144" t="str">
-        <v>HAART</v>
+        <v>MaHAART</v>
       </c>
       <c r="G144" t="str">
         <v>Is the mother on HAART?</v>
@@ -10215,7 +10215,7 @@
         <v>LengthHAART</v>
       </c>
       <c r="G145" t="str">
-        <v>Mother on HAART since when?</v>
+        <v>Maternal HAART Initiation</v>
       </c>
       <c r="H145" t="str">
         <v>dropdown</v>
@@ -10233,7 +10233,7 @@
         <v>No</v>
       </c>
       <c r="M145" t="str">
-        <v>$HAART = 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N145" t="str">
         <v>[{"value":"1stTrim","valueLabel":"1st Trimester or earlier"},{"value":"2ndTrim","valueLabel":"2nd Trimester"},{"value":"3rdTrim","valueLabel":"3rd Trimester more than 1 month before delivery"},{"value":"Late","valueLabel":"Less than 1 month before delivery"},{"value":"U","valueLabel":"Unknown"}]</v>
@@ -10301,7 +10301,7 @@
         <v>No</v>
       </c>
       <c r="M146" t="str">
-        <v>$HAART= 'Y'</v>
+        <v>$MaHAART = 'Y'</v>
       </c>
       <c r="N146" t="str">
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NA","valueLabel":"Not applicable"}]</v>
@@ -10351,7 +10351,7 @@
         <v>VLNumber</v>
       </c>
       <c r="G147" t="str">
-        <v>Viral Load</v>
+        <v>Viral Load (copies/ml)</v>
       </c>
       <c r="H147" t="str">
         <v>number</v>
@@ -10573,13 +10573,13 @@
         <v>No</v>
       </c>
       <c r="M150" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N150" t="str">
         <v>[{"value":"Y","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O150" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P150" t="str">
         <v/>
@@ -11117,13 +11117,13 @@
         <v>No</v>
       </c>
       <c r="M158" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N158" t="str">
         <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DM","valueLabel":"Diabetes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HD","valueLabel":"Heart disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HTN","valueLabel":"Hypertension or pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"STD","valueLabel":"Sexually Transmitted Disease (other than HIV/syphilis)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"THY","valueLabel":"Thyroid disease / goitre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TU","valueLabel":"Tuberculosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Unknown","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O158" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P158" t="str">
         <v/>
@@ -11259,7 +11259,7 @@
         <v/>
       </c>
       <c r="O160" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P160" t="str">
         <v/>
@@ -11327,7 +11327,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O161" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P161" t="str">
         <v/>
@@ -11395,7 +11395,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O162" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P162" t="str">
         <v/>
@@ -11463,7 +11463,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"U","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O163" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P163" t="str">
         <v/>
@@ -11525,13 +11525,13 @@
         <v>No</v>
       </c>
       <c r="M164" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N164" t="str">
         <v>[{"value":"Y","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"N","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"U","valueLabel":"Not Sure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O164" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P164" t="str">
         <v/>
@@ -11593,13 +11593,13 @@
         <v>No</v>
       </c>
       <c r="M165" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N165" t="str">
         <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"SVB","valueLabel":"Significant Vaginal Bleeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O165" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P165" t="str">
         <v/>
@@ -11667,7 +11667,7 @@
         <v>[{"value":"NOPROM","valueLabel":"Less than 18 hours"},{"value":"PROM","valueLabel":"Greater than 18 hours"}]</v>
       </c>
       <c r="O166" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P166" t="str">
         <v/>
@@ -11729,13 +11729,13 @@
         <v>No</v>
       </c>
       <c r="M167" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N167" t="str">
-        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O167" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P167" t="str">
         <v/>
@@ -11803,7 +11803,7 @@
         <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"Unk","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O168" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P168" t="str">
         <v/>
@@ -11871,7 +11871,7 @@
         <v>[{"value":"1","valueLabel":"Spontaneous Vaginal Delivery"},{"value":"7","valueLabel":"Induced Vaginal Delivery"},{"value":"6","valueLabel":"Breech extraction (vaginal)"},{"value":"2","valueLabel":"Vacuum extraction"},{"value":"3","valueLabel":"Forceps extraction"},{"value":"4","valueLabel":"Elective Ceasarian Section (ELCS)"},{"value":"5","valueLabel":"Emergency Ceasarian Section (EMCS)"}]</v>
       </c>
       <c r="O169" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P169" t="str">
         <v/>
@@ -12069,13 +12069,13 @@
         <v>No</v>
       </c>
       <c r="M172" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N172" t="str">
         <v>[{"value":"Stim","valueLabel":"Stimulation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Suc","valueLabel":"Suctioning","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O2","valueLabel":"Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BVM","valueLabel":"Bag Valve Mask Ventilation (BVM)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPR","valueLabel":"Cardio Pulmonary Resuscitation (CPR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O172" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P172" t="str">
         <v/>
@@ -12273,13 +12273,13 @@
         <v>No</v>
       </c>
       <c r="M175" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="N175" t="str">
         <v>[{"value":"DCC","valueLabel":"Delayed Cord Clamping (greater than 60 secs)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"S2S","valueLabel":"Skin to Skin (within 1st hour of life)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast Feeding (within 1st hour of life)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"U","valueLabel":"Unknown","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O175" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU' or $ReferredFrom2 = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')] or $ReferredFrom2 = 'DU')</v>
       </c>
       <c r="P175" t="str">
         <v/>
@@ -12347,7 +12347,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
       </c>
       <c r="O176" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P176" t="str">
         <v/>
@@ -12415,7 +12415,7 @@
         <v>[{"value":"Y","valueLabel":"Yes"},{"value":"N","valueLabel":"No"},{"value":"NS","valueLabel":"Not Sure"}]</v>
       </c>
       <c r="O177" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="P177" t="str">
         <v/>
@@ -14248,7 +14248,7 @@
         <v/>
       </c>
       <c r="N204" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BI","valueLabel":"Birth Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NSep","valueLabel":"Suspected neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis (Not symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32 to 37 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31+6 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UH","valueLabel":"Umbilical Hernia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConTet","valueLabel":"Consider Tetanus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ApofPrem","valueLabel":"Apnoea of prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NecEnt","valueLabel":"Consider Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConMen","valueLabel":"Consider Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born before arrival","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BT","valueLabel":"Birth injury / Trauma","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cong","valueLabel":"Congenital Abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Conv","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dhyd","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DF","valueLabel":"Difficulty Feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DUM","valueLabel":"Abandoned baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVU","valueLabel":"HIV Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GSchis","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MJ","valueLabel":"Physiological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Possible Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiHypo","valueLabel":"Mild Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ModHypo","valueLabel":"Moderate Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHypo","valueLabel":"Severe Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Hyperth","valueLabel":"Hyperthermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NSep","valueLabel":"Suspected neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Risk","valueLabel":"Risk factors for sepsis (Not symptomatic)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NB","valueLabel":"Normal Baby","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia /  Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Premature (32 to 37 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"VPrem","valueLabel":"Very Premature (28-31+6 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Safe","valueLabel":"Safekeeping","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DJ","valueLabel":"Pathological Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ProJ","valueLabel":"Prolonged Jaundice","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftLip","valueLabel":"Cleft lip","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CleftPal","valueLabel":"Cleft palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Omph","valueLabel":"Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Myelo","valueLabel":"Myelomeningocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Syph_Exp","valueLabel":"Syphilis exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UH","valueLabel":"Umbilical Hernia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConTet","valueLabel":"Consider Tetanus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ApofPrem","valueLabel":"Apnoea of prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NecEnt","valueLabel":"Consider Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ConMen","valueLabel":"Consider Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIVExp","valueLabel":"HIV Exposed","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O204" t="str">
         <v/>
@@ -14319,7 +14319,7 @@
         <v/>
       </c>
       <c r="O205" t="str">
-        <v>($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $Diagnoses = 'RDN' or $AdmReason = 'PREMRDS') and $NobCPAP = false</v>
+        <v>($DangerSigns = 'Grun' or $RR &gt; 60 or $SatsO2 &lt; 90 or $WOB = 'Mod' or $WOB = 'Sev' or $AdmReason = 'PREMRDS')</v>
       </c>
       <c r="P205" t="str">
         <v/>
@@ -14452,7 +14452,7 @@
         <v/>
       </c>
       <c r="N207" t="str">
-        <v>[{"value":"ICU","valueLabel":"Admit to ICU","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PREM","valueLabel":"Admit to Prem 1","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AdOb","valueLabel":"Admit to Observation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Surg","valueLabel":"Admit to surgical","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TA","valueLabel":"Admit to transit A","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Warm","valueLabel":"Keep warm with hat, bootees etc","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"KMC","valueLabel":"Kangaroo mother care","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Obs","valueLabel":"Observations 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Incub","valueLabel":"Nurse in incubator","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PTX","valueLabel":"Phototherapy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IntVe","valueLabel":"Intubate and Ventilate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NC02","valueLabel":"Nasal Cannulae Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast feed freely","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPAP","valueLabel":"CPAP","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cup","valueLabel":"Breast feed with cup top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NG","valueLabel":"Breast feed with NG top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NGX","valueLabel":"NG feed exclusively","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OGX","valueLabel":"OGT feed exclusively","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IVI","valueLabel":"Maintenance Iv fluids (add rate)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SBR","valueLabel":"Check bilirubin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FBC","valueLabel":"Check FBC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BC","valueLabel":"Blood culture","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DNA","valueLabel":"DNA PCR for HIV","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MatSy","valueLabel":"Maternal Syphillis testing","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAT","valueLabel":"Maternal PITC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gluc","valueLabel":"Check glucose stat then 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Renal","valueLabel":"Check renal function","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Neuro","valueLabel":"Consult neurosurgeon on call","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ortho","valueLabel":"Consult orthopaedic surgeon on call","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Paeds","valueLabel":"Consult paediatric surgeon on call","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Couns","valueLabel":"Counsel caregivers","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GUA","valueLabel":"Guarded Prognosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NPO","valueLabel":"Keep nil by mouth","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TORCH","valueLabel":"TORCH screen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AMIN","valueLabel":"Aminophylline","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AZT","valueLabel":"AZT","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Caff","valueLabel":"Caffeine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Amik","valueLabel":"Amikacin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Amp","valueLabel":"Ampicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cef","valueLabel":"Ceftriaxone (surgical)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gent","valueLabel":"Gentamicin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Xpen","valueLabel":"X Penicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Met","valueLabel":"Metronidazole","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NVP","valueLabel":"Nevirapine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"OTHER","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"ICU","valueLabel":"ICU","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PREM","valueLabel":"Admit to Prem 1","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AdOb","valueLabel":"Admit to Observation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Surg","valueLabel":"Admit to surgical","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TA","valueLabel":"Admit to transit A","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Warm","valueLabel":"Keep warm with hat, bootees etc","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"KMC","valueLabel":"Kangaroo mother care","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Obs","valueLabel":"Observations 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Incub","valueLabel":"Nurse in incubator","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PTX","valueLabel":"Phototherapy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IntVe","valueLabel":"Intubate and Ventilate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NC02","valueLabel":"Nasal Cannulae Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast feed freely","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPAP","valueLabel":"CPAP","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cup","valueLabel":"Breast feed with cup top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NG","valueLabel":"Breast feed with NG top ups","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NGX","valueLabel":"NG feed exclusively","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OGX","valueLabel":"OGT feed exclusively","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IVI","valueLabel":"Maintenance Iv fluids (add rate)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SBR","valueLabel":"Check bilirubin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FBC","valueLabel":"Check FBC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BC","valueLabel":"Blood culture","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DNA","valueLabel":"DNA PCR for HIV","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MatSy","valueLabel":"Maternal Syphillis testing","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAT","valueLabel":"Maternal PITC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gluc","valueLabel":"Check glucose stat then 4 hourly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Renal","valueLabel":"Check renal function","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Neuro","valueLabel":"Consult neurosurgeon on call","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ortho","valueLabel":"Consult orthopaedic surgeon on call","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Paeds","valueLabel":"Consult paediatric surgeon on call","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Couns","valueLabel":"Counsel caregivers","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GUA","valueLabel":"Guarded Prognosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NPO","valueLabel":"Keep nil by mouth","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TORCH","valueLabel":"TORCH screen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AMIN","valueLabel":"Aminophylline","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AZT","valueLabel":"AZT","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Caff","valueLabel":"Caffeine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Amik","valueLabel":"Amikacin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Amp","valueLabel":"Ampicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cef","valueLabel":"Ceftriaxone (surgical)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gent","valueLabel":"Gentamicin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Xpen","valueLabel":"X Penicillin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Met","valueLabel":"Metronidazole","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NVP","valueLabel":"Nevirapine","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"OTHER","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O207" t="str">
         <v/>
@@ -15347,7 +15347,7 @@
         <v>Sally Mugabe Central Hospital</v>
       </c>
       <c r="C3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="D3" t="str">
         <v>Born before arrival</v>
@@ -15359,7 +15359,7 @@
         <v>e3cb5ede-7fc1-43aa-8d79-bd36a4cd332e</v>
       </c>
       <c r="G3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="H3" t="str">
         <v>6992</v>
@@ -15404,7 +15404,7 @@
         <v>BBA</v>
       </c>
       <c r="V3" t="str">
-        <v>Born Before Arrival</v>
+        <v>Born before arrival</v>
       </c>
       <c r="W3" t="str">
         <v/>
@@ -15424,19 +15424,19 @@
         <v>Sally Mugabe Central Hospital</v>
       </c>
       <c r="C4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="D4" t="str">
         <v>Birth Trauma</v>
       </c>
       <c r="E4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="F4" t="str">
         <v>ec2adc2a-3fa6-438d-89de-7e3b87f568c6</v>
       </c>
       <c r="G4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="H4" t="str">
         <v>6993</v>
@@ -15478,10 +15478,10 @@
         <v>diagnosis</v>
       </c>
       <c r="U4" t="str">
-        <v>BI</v>
+        <v>BT</v>
       </c>
       <c r="V4" t="str">
-        <v>Birth Trauma</v>
+        <v>Birth injury / Trauma</v>
       </c>
       <c r="W4" t="str">
         <v/>
@@ -17794,7 +17794,7 @@
         <v>Sally Mugabe Central Hospital</v>
       </c>
       <c r="C31" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="D31" t="str">
         <v>RDN - Congenital Pneumonia</v>
@@ -17806,7 +17806,7 @@
         <v>2f74e32f-d1a8-4a5a-b672-cee9b6d6fd38</v>
       </c>
       <c r="G31" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="H31" t="str">
         <v>7020</v>
@@ -17868,7 +17868,7 @@
         <v>CongPneu</v>
       </c>
       <c r="V31" t="str">
-        <v>? Congenital Pneumonia</v>
+        <v>Congenital Pneumonia</v>
       </c>
       <c r="W31" t="str">
         <v/>
